--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.04086588069245</v>
+        <v>3.094140705612524</v>
       </c>
       <c r="D2" t="n">
-        <v>19.06933286123063</v>
+        <v>3.098766589949977</v>
       </c>
       <c r="E2" t="n">
-        <v>4.601201177215913</v>
+        <v>0.7476951912975858</v>
       </c>
       <c r="F2" t="n">
-        <v>4.267335764513325</v>
+        <v>0.6934420617334154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.24454557555093</v>
+        <v>1.664738656027026</v>
       </c>
       <c r="D3" t="n">
-        <v>10.7290405614395</v>
+        <v>1.743469091233919</v>
       </c>
       <c r="E3" t="n">
-        <v>4.601201177215913</v>
+        <v>0.7476951912975858</v>
       </c>
       <c r="F3" t="n">
-        <v>4.267335764513325</v>
+        <v>0.6934420617334154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.86590309481798</v>
+        <v>3.715709252907923</v>
       </c>
       <c r="D4" t="n">
-        <v>22.43457643899931</v>
+        <v>3.645618671337388</v>
       </c>
       <c r="E4" t="n">
-        <v>4.601201177215913</v>
+        <v>0.7476951912975858</v>
       </c>
       <c r="F4" t="n">
-        <v>4.267335764513325</v>
+        <v>0.6934420617334154</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.48887101969136</v>
+        <v>3.004441540699847</v>
       </c>
       <c r="D5" t="n">
-        <v>17.93462190757366</v>
+        <v>2.914376059980721</v>
       </c>
       <c r="E5" t="n">
-        <v>4.601201177215913</v>
+        <v>0.7476951912975858</v>
       </c>
       <c r="F5" t="n">
-        <v>4.267335764513325</v>
+        <v>0.6934420617334154</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
